--- a/artfynd/A 33969-2026 artfynd.xlsx
+++ b/artfynd/A 33969-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136088365</v>
       </c>
       <c r="B2" t="n">
-        <v>80558</v>
+        <v>80559</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -896,7 +896,7 @@
         <v>136088399</v>
       </c>
       <c r="B4" t="n">
-        <v>99328</v>
+        <v>99329</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -998,7 +998,7 @@
         <v>136088261</v>
       </c>
       <c r="B5" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1109,7 +1109,7 @@
         <v>136088454</v>
       </c>
       <c r="B6" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1220,7 +1220,7 @@
         <v>136088807</v>
       </c>
       <c r="B7" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1331,7 +1331,7 @@
         <v>136089082</v>
       </c>
       <c r="B8" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1442,7 +1442,7 @@
         <v>136089236</v>
       </c>
       <c r="B9" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1553,7 +1553,7 @@
         <v>136089393</v>
       </c>
       <c r="B10" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 33969-2026 artfynd.xlsx
+++ b/artfynd/A 33969-2026 artfynd.xlsx
@@ -896,7 +896,7 @@
         <v>136088399</v>
       </c>
       <c r="B4" t="n">
-        <v>99329</v>
+        <v>99330</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -998,7 +998,7 @@
         <v>136088261</v>
       </c>
       <c r="B5" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1109,7 +1109,7 @@
         <v>136088454</v>
       </c>
       <c r="B6" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1220,7 +1220,7 @@
         <v>136088807</v>
       </c>
       <c r="B7" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1331,7 +1331,7 @@
         <v>136089082</v>
       </c>
       <c r="B8" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1442,7 +1442,7 @@
         <v>136089236</v>
       </c>
       <c r="B9" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1553,7 +1553,7 @@
         <v>136089393</v>
       </c>
       <c r="B10" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 33969-2026 artfynd.xlsx
+++ b/artfynd/A 33969-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136088365</v>
       </c>
       <c r="B2" t="n">
-        <v>80559</v>
+        <v>80560</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136088296</v>
       </c>
       <c r="B3" t="n">
-        <v>57169</v>
+        <v>57170</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -896,7 +896,7 @@
         <v>136088399</v>
       </c>
       <c r="B4" t="n">
-        <v>99330</v>
+        <v>99331</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -998,7 +998,7 @@
         <v>136088261</v>
       </c>
       <c r="B5" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1109,7 +1109,7 @@
         <v>136088454</v>
       </c>
       <c r="B6" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1220,7 +1220,7 @@
         <v>136088807</v>
       </c>
       <c r="B7" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1331,7 +1331,7 @@
         <v>136089082</v>
       </c>
       <c r="B8" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1442,7 +1442,7 @@
         <v>136089236</v>
       </c>
       <c r="B9" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1553,7 +1553,7 @@
         <v>136089393</v>
       </c>
       <c r="B10" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 33969-2026 artfynd.xlsx
+++ b/artfynd/A 33969-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136088365</v>
       </c>
       <c r="B2" t="n">
-        <v>80560</v>
+        <v>80564</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136088296</v>
       </c>
       <c r="B3" t="n">
-        <v>57170</v>
+        <v>57174</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -896,7 +896,7 @@
         <v>136088399</v>
       </c>
       <c r="B4" t="n">
-        <v>99331</v>
+        <v>99337</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -998,7 +998,7 @@
         <v>136088261</v>
       </c>
       <c r="B5" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1109,7 +1109,7 @@
         <v>136088454</v>
       </c>
       <c r="B6" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1220,7 +1220,7 @@
         <v>136088807</v>
       </c>
       <c r="B7" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1331,7 +1331,7 @@
         <v>136089082</v>
       </c>
       <c r="B8" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1442,7 +1442,7 @@
         <v>136089236</v>
       </c>
       <c r="B9" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1553,7 +1553,7 @@
         <v>136089393</v>
       </c>
       <c r="B10" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 33969-2026 artfynd.xlsx
+++ b/artfynd/A 33969-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136088365</v>
       </c>
       <c r="B2" t="n">
-        <v>80564</v>
+        <v>80565</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136088296</v>
       </c>
       <c r="B3" t="n">
-        <v>57174</v>
+        <v>57175</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -896,7 +896,7 @@
         <v>136088399</v>
       </c>
       <c r="B4" t="n">
-        <v>99337</v>
+        <v>99338</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -998,7 +998,7 @@
         <v>136088261</v>
       </c>
       <c r="B5" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1109,7 +1109,7 @@
         <v>136088454</v>
       </c>
       <c r="B6" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1220,7 +1220,7 @@
         <v>136088807</v>
       </c>
       <c r="B7" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1331,7 +1331,7 @@
         <v>136089082</v>
       </c>
       <c r="B8" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1442,7 +1442,7 @@
         <v>136089236</v>
       </c>
       <c r="B9" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1553,7 +1553,7 @@
         <v>136089393</v>
       </c>
       <c r="B10" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 33969-2026 artfynd.xlsx
+++ b/artfynd/A 33969-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136088365</v>
       </c>
       <c r="B2" t="n">
-        <v>80565</v>
+        <v>80569</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -896,7 +896,7 @@
         <v>136088399</v>
       </c>
       <c r="B4" t="n">
-        <v>99338</v>
+        <v>99349</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -998,7 +998,7 @@
         <v>136088261</v>
       </c>
       <c r="B5" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1109,7 +1109,7 @@
         <v>136088454</v>
       </c>
       <c r="B6" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1220,7 +1220,7 @@
         <v>136088807</v>
       </c>
       <c r="B7" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1331,7 +1331,7 @@
         <v>136089082</v>
       </c>
       <c r="B8" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1442,7 +1442,7 @@
         <v>136089236</v>
       </c>
       <c r="B9" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1553,7 +1553,7 @@
         <v>136089393</v>
       </c>
       <c r="B10" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 33969-2026 artfynd.xlsx
+++ b/artfynd/A 33969-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136088365</v>
       </c>
       <c r="B2" t="n">
-        <v>80569</v>
+        <v>80575</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136088296</v>
       </c>
       <c r="B3" t="n">
-        <v>57175</v>
+        <v>57180</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -896,7 +896,7 @@
         <v>136088399</v>
       </c>
       <c r="B4" t="n">
-        <v>99349</v>
+        <v>99362</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -998,7 +998,7 @@
         <v>136088261</v>
       </c>
       <c r="B5" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1109,7 +1109,7 @@
         <v>136088454</v>
       </c>
       <c r="B6" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1220,7 +1220,7 @@
         <v>136088807</v>
       </c>
       <c r="B7" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1331,7 +1331,7 @@
         <v>136089082</v>
       </c>
       <c r="B8" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1442,7 +1442,7 @@
         <v>136089236</v>
       </c>
       <c r="B9" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1553,7 +1553,7 @@
         <v>136089393</v>
       </c>
       <c r="B10" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 33969-2026 artfynd.xlsx
+++ b/artfynd/A 33969-2026 artfynd.xlsx
@@ -896,7 +896,7 @@
         <v>136088399</v>
       </c>
       <c r="B4" t="n">
-        <v>99362</v>
+        <v>99363</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -998,7 +998,7 @@
         <v>136088261</v>
       </c>
       <c r="B5" t="n">
-        <v>99327</v>
+        <v>99328</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1109,7 +1109,7 @@
         <v>136088454</v>
       </c>
       <c r="B6" t="n">
-        <v>99327</v>
+        <v>99328</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1220,7 +1220,7 @@
         <v>136088807</v>
       </c>
       <c r="B7" t="n">
-        <v>99327</v>
+        <v>99328</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1331,7 +1331,7 @@
         <v>136089082</v>
       </c>
       <c r="B8" t="n">
-        <v>99327</v>
+        <v>99328</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1442,7 +1442,7 @@
         <v>136089236</v>
       </c>
       <c r="B9" t="n">
-        <v>99327</v>
+        <v>99328</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1553,7 +1553,7 @@
         <v>136089393</v>
       </c>
       <c r="B10" t="n">
-        <v>99327</v>
+        <v>99328</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 33969-2026 artfynd.xlsx
+++ b/artfynd/A 33969-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136088365</v>
       </c>
       <c r="B2" t="n">
-        <v>80575</v>
+        <v>80588</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136088296</v>
       </c>
       <c r="B3" t="n">
-        <v>57180</v>
+        <v>57193</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -896,7 +896,7 @@
         <v>136088399</v>
       </c>
       <c r="B4" t="n">
-        <v>99363</v>
+        <v>99376</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -998,7 +998,7 @@
         <v>136088261</v>
       </c>
       <c r="B5" t="n">
-        <v>99328</v>
+        <v>99341</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1109,7 +1109,7 @@
         <v>136088454</v>
       </c>
       <c r="B6" t="n">
-        <v>99328</v>
+        <v>99341</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1220,7 +1220,7 @@
         <v>136088807</v>
       </c>
       <c r="B7" t="n">
-        <v>99328</v>
+        <v>99341</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1331,7 +1331,7 @@
         <v>136089082</v>
       </c>
       <c r="B8" t="n">
-        <v>99328</v>
+        <v>99341</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1442,7 +1442,7 @@
         <v>136089236</v>
       </c>
       <c r="B9" t="n">
-        <v>99328</v>
+        <v>99341</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1553,7 +1553,7 @@
         <v>136089393</v>
       </c>
       <c r="B10" t="n">
-        <v>99328</v>
+        <v>99341</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 33969-2026 artfynd.xlsx
+++ b/artfynd/A 33969-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136088365</v>
       </c>
       <c r="B2" t="n">
-        <v>80588</v>
+        <v>80589</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -896,7 +896,7 @@
         <v>136088399</v>
       </c>
       <c r="B4" t="n">
-        <v>99376</v>
+        <v>99377</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -998,7 +998,7 @@
         <v>136088261</v>
       </c>
       <c r="B5" t="n">
-        <v>99341</v>
+        <v>99342</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1109,7 +1109,7 @@
         <v>136088454</v>
       </c>
       <c r="B6" t="n">
-        <v>99341</v>
+        <v>99342</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1220,7 +1220,7 @@
         <v>136088807</v>
       </c>
       <c r="B7" t="n">
-        <v>99341</v>
+        <v>99342</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1331,7 +1331,7 @@
         <v>136089082</v>
       </c>
       <c r="B8" t="n">
-        <v>99341</v>
+        <v>99342</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1442,7 +1442,7 @@
         <v>136089236</v>
       </c>
       <c r="B9" t="n">
-        <v>99341</v>
+        <v>99342</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1553,7 +1553,7 @@
         <v>136089393</v>
       </c>
       <c r="B10" t="n">
-        <v>99341</v>
+        <v>99342</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
